--- a/artfynd/A 44362-2023 artfynd.xlsx
+++ b/artfynd/A 44362-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115660409</v>
+        <v>115660388</v>
       </c>
       <c r="B8" t="n">
-        <v>96604</v>
+        <v>57265</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,34 +1309,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>314569</v>
+        <v>314491</v>
       </c>
       <c r="R8" t="n">
-        <v>6525420</v>
+        <v>6525273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,13 +1379,17 @@
           <t>2024-03-31</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med gott om gammal kåda som runnit ner längs med stammen</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1396,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115660388</v>
+        <v>115660390</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
+        <v>56478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,42 +1420,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>314491</v>
+        <v>314673</v>
       </c>
       <c r="R9" t="n">
-        <v>6525273</v>
+        <v>6525528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,7 +1488,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall med gott om gammal kåda som runnit ner längs med stammen</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115660390</v>
+        <v>115660395</v>
       </c>
       <c r="B10" t="n">
-        <v>56478</v>
+        <v>57281</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>314673</v>
+        <v>314549</v>
       </c>
       <c r="R10" t="n">
-        <v>6525528</v>
+        <v>6525366</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115660395</v>
+        <v>115660416</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
+        <v>94429</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1626,25 +1634,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>314549</v>
+        <v>314428</v>
       </c>
       <c r="R11" t="n">
-        <v>6525366</v>
+        <v>6525272</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,11 +1698,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-03-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115660416</v>
+        <v>115660406</v>
       </c>
       <c r="B12" t="n">
-        <v>94429</v>
+        <v>57281</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,25 +1736,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>314428</v>
+        <v>314648</v>
       </c>
       <c r="R12" t="n">
-        <v>6525272</v>
+        <v>6525330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,6 +1800,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115660406</v>
+        <v>115660394</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
+        <v>95923</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,25 +1843,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1863,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>314648</v>
+        <v>314608</v>
       </c>
       <c r="R13" t="n">
-        <v>6525330</v>
+        <v>6525515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,17 +1909,13 @@
           <t>2024-03-31</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1930,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115660394</v>
+        <v>115660401</v>
       </c>
       <c r="B14" t="n">
-        <v>95923</v>
+        <v>57281</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1942,25 +1946,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>314608</v>
+        <v>314536</v>
       </c>
       <c r="R14" t="n">
-        <v>6525515</v>
+        <v>6525262</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,13 +2012,17 @@
           <t>2024-03-31</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2033,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115660401</v>
+        <v>115660408</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
+        <v>96610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,25 +2053,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>314536</v>
+        <v>314673</v>
       </c>
       <c r="R15" t="n">
-        <v>6525262</v>
+        <v>6525525</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-03-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115660408</v>
+        <v>115660392</v>
       </c>
       <c r="B16" t="n">
-        <v>96610</v>
+        <v>95923</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2180,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>314673</v>
+        <v>314391</v>
       </c>
       <c r="R16" t="n">
-        <v>6525525</v>
+        <v>6525476</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115660392</v>
+        <v>115660405</v>
       </c>
       <c r="B17" t="n">
-        <v>95923</v>
+        <v>57281</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,25 +2257,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2282,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>314391</v>
+        <v>314629</v>
       </c>
       <c r="R17" t="n">
-        <v>6525476</v>
+        <v>6525488</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,6 +2321,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2344,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115660405</v>
+        <v>115660386</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
+        <v>94069</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,25 +2364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2384,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>314629</v>
+        <v>314633</v>
       </c>
       <c r="R18" t="n">
-        <v>6525488</v>
+        <v>6525333</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,11 +2428,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-03-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,7 +2454,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115660386</v>
+        <v>115660381</v>
       </c>
       <c r="B19" t="n">
         <v>94069</v>
@@ -2491,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>314633</v>
+        <v>314399</v>
       </c>
       <c r="R19" t="n">
-        <v>6525333</v>
+        <v>6525319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115660381</v>
+        <v>115660402</v>
       </c>
       <c r="B20" t="n">
-        <v>94069</v>
+        <v>57281</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2565,25 +2568,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>314399</v>
+        <v>314661</v>
       </c>
       <c r="R20" t="n">
-        <v>6525319</v>
+        <v>6525395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,6 +2632,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2655,7 +2663,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115660402</v>
+        <v>115660403</v>
       </c>
       <c r="B21" t="n">
         <v>57281</v>
@@ -2695,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>314661</v>
+        <v>314575</v>
       </c>
       <c r="R21" t="n">
-        <v>6525395</v>
+        <v>6525376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,113 +2767,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>115660403</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Holane, Dls</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>314575</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6525376</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Töftedal</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-03-31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44362-2023 artfynd.xlsx
+++ b/artfynd/A 44362-2023 artfynd.xlsx
@@ -1091,11 +1091,11 @@
         <v>115660415</v>
       </c>
       <c r="B6" t="n">
-        <v>57271</v>
+        <v>57389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 44362-2023 artfynd.xlsx
+++ b/artfynd/A 44362-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>115660415</v>
       </c>
       <c r="B6" t="n">
-        <v>57389</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
